--- a/artfynd/A 2089-2026 artfynd.xlsx
+++ b/artfynd/A 2089-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>77211847</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520567.6650946115</v>
+        <v>520568</v>
       </c>
       <c r="R2" t="n">
-        <v>6759503.50322478</v>
+        <v>6759504</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -799,32 +794,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>77442116</v>
+        <v>77211828</v>
       </c>
       <c r="B3" t="n">
-        <v>57987</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103008</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,10 +828,14 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -876,22 +875,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-04-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-04-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,6 +914,251 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>59152335</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>långnäset, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>520568</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6759504</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2016-04-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2016-04-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Teresia Holmberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Teresia Holmberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>77442116</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58286</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>långnäset, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>520568</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6759504</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-05-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Teresia Holmberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Teresia Holmberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2089-2026 artfynd.xlsx
+++ b/artfynd/A 2089-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77211847</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77211828</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1040,6 +1055,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59152335</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1159,8 +1179,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77442116</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>